--- a/tests/fixtures/extract_corpus_v2/dev/bundle_vv40_fea_003/extracted.xlsx
+++ b/tests/fixtures/extract_corpus_v2/dev/bundle_vv40_fea_003/extracted.xlsx
@@ -490,6 +490,11 @@
         <t>[Extract] | Confidence: 50%</t>
       </text>
     </comment>
+    <comment ref="K3" authorId="0" shapeId="0">
+      <text>
+        <t>[Extract] | Confidence: 50%</t>
+      </text>
+    </comment>
     <comment ref="L3" authorId="0" shapeId="0">
       <text>
         <t>[Extract] | Confidence: 50%</t>
@@ -1383,12 +1388,12 @@
       </c>
       <c r="B3" s="39" t="inlineStr">
         <is>
-          <t>Quasi-static stress margin and modal clearance prediction for AVB-21 avionics tray bracket under launch loads</t>
+          <t>Quasi-static and modal FEA of AVB-21 avionics tray bracket for launch vehicle qualification</t>
         </is>
       </c>
       <c r="C3" s="39" t="inlineStr">
         <is>
-          <t>FEA of an aluminum L-bracket (AA 7075-T6) subjected to 15 g axial and 8 g lateral quasi-static equivalent accelerations and qualification vibration. The model is used to confirm yield margin at stress hot-spots around bolt holes and fillets, and to verify that the first three natural frequencies clear the payload bay notch lines. Toolchain is Abaqus/Standard 2023 HF7 on RHEL 8 with CAD from NX 2206.</t>
+          <t>Finite element analysis of an aluminum L-bracket (AA 7075-T6) subjected to quasi-static g-loads and qualification vibration. The model is used to confirm yield margin at stress hot-spots around bolt holes and fillets, and to verify that the first three natural frequencies clear the payload bay frequency exclusion line at 750 Hz. Toolchain is Abaqus/Standard 2023 HF7. Validation against shaker modal test and static strain-gage pull test.</t>
         </is>
       </c>
       <c r="D3" s="39" t="inlineStr">
@@ -1426,9 +1431,9 @@
           <t>Date of this assessment (YYYY-MM-DD)</t>
         </is>
       </c>
-      <c r="K3" s="22" t="inlineStr">
-        <is>
-          <t>DOI, report number, or URI</t>
+      <c r="K3" s="39" t="inlineStr">
+        <is>
+          <t>report.md</t>
         </is>
       </c>
       <c r="L3" s="40" t="inlineStr">
@@ -2024,7 +2029,7 @@
       </c>
       <c r="B3" s="39" t="inlineStr">
         <is>
-          <t>Yield Margin and Modal Clearance Requirements</t>
+          <t>Yield Margin and Modal Clearance Requirement</t>
         </is>
       </c>
       <c r="C3" s="22" t="inlineStr">
@@ -2034,7 +2039,7 @@
       </c>
       <c r="D3" s="39" t="inlineStr">
         <is>
-          <t>Bracket must maintain positive yield margin (FoS &gt;1.25 on yield) at all hot-spots under design loads, and first three natural frequencies must clear the 750 Hz payload bay notch line by at least 10%.</t>
+          <t>Bracket must maintain positive yield margin (FoS &gt; specified minimum) at all stress hot-spots under 15 g axial and 8 g lateral quasi-static loads, and first three natural frequencies must clear the 750 Hz payload bay notch line by at least 10%.</t>
         </is>
       </c>
       <c r="E3" s="22" t="inlineStr">
@@ -2062,7 +2067,7 @@
       <c r="C4" s="24" t="n"/>
       <c r="D4" s="41" t="inlineStr">
         <is>
-          <t>Abaqus/Standard nonlinear static model with bolt pretension, contact, and bilinear plasticity for yield margin assessment.</t>
+          <t>Abaqus/Standard 2023 HF7 nonlinear static model with bolt pretension, contact, and bilinear kinematic plasticity for AA 7075-T6; C3D10M quadratic tet elements; symmetry half-model.</t>
         </is>
       </c>
       <c r="E4" s="33" t="n"/>
@@ -2076,13 +2081,13 @@
       </c>
       <c r="B5" s="41" t="inlineStr">
         <is>
-          <t>AVB21 Modal Analysis Model</t>
+          <t>AVB21 Modal FEA Model</t>
         </is>
       </c>
       <c r="C5" s="24" t="n"/>
       <c r="D5" s="41" t="inlineStr">
         <is>
-          <t>Abaqus/Standard linear perturbation modal model with tied interfaces and temperature-dependent elastic modulus for natural frequency prediction.</t>
+          <t>Abaqus/Standard 2023 HF7 linear perturbation modal model about prestressed state with tied interfaces; temperature-dependent elastic modulus sweep (20 C / 40 C).</t>
         </is>
       </c>
       <c r="E5" s="33" t="n"/>
@@ -2096,13 +2101,13 @@
       </c>
       <c r="B6" s="41" t="inlineStr">
         <is>
-          <t>Shaker Test and Static Pull Test Data</t>
+          <t>Shaker Modal Test and Static Pull Test Data</t>
         </is>
       </c>
       <c r="C6" s="24" t="n"/>
       <c r="D6" s="41" t="inlineStr">
         <is>
-          <t>Measured natural frequencies (f1=770 Hz, f2=1130 Hz, f3=1592 Hz) from shaker test and strain gauge readings (SG-03, SG-07) from static pull test at 15 g equivalent loading.</t>
+          <t>Laboratory shaker test (full bracket, four bolts at 5.7 N·m, helicoils and Belleville washers installed) measuring first three natural frequencies and static strain-gage readings at 15 g equivalent load.</t>
         </is>
       </c>
       <c r="E6" s="33" t="n"/>
@@ -2116,13 +2121,13 @@
       </c>
       <c r="B7" s="41" t="inlineStr">
         <is>
-          <t>Material Coupon Data</t>
+          <t>AA 7075-T6 Material Coupon Data</t>
         </is>
       </c>
       <c r="C7" s="24" t="n"/>
       <c r="D7" s="41" t="inlineStr">
         <is>
-          <t>In-house ASTM E8 tensile coupons for AA 7075-T6 used to calibrate bilinear plasticity curve (Etan ~1.2 GPa); supplemented by MIL-HDBK-5 temperature-dependent modulus tables.</t>
+          <t>In-house tensile coupon data per ASTM E8 used to calibrate bilinear kinematic plasticity curve (Etan ~1.2 GPa, Ramberg-Osgood n=8.7); elastic properties from AMS 4045 and temperature-dependent E from MIL-HDBK-5.</t>
         </is>
       </c>
       <c r="E7" s="33" t="n"/>
@@ -2279,12 +2284,12 @@
       </c>
       <c r="D3" s="39" t="inlineStr">
         <is>
-          <t>Three mesh densities (coarse ~78k, medium ~164k, fine ~512k elements) compared for peak von Mises stress at lower bolt hole and tip deflection. Richardson extrapolation performed on medium/fine pair only to estimate zero-mesh-size stress of 244 MPa.</t>
+          <t>Three-level h-refinement study (coarse ~78k, medium ~164k, fine ~512k C3D10M elements) comparing peak von Mises stress at lower bolt hole and tip deflection across mesh densities. Richardson extrapolation performed on medium/fine pair to estimate zero-mesh-size stress.</t>
         </is>
       </c>
       <c r="E3" s="39" t="inlineStr">
         <is>
-          <t>Richardson extrapolation reference value (244 MPa)</t>
+          <t>Richardson extrapolation extrapolated stress of 244 MPa</t>
         </is>
       </c>
       <c r="F3" s="39" t="inlineStr">
@@ -2299,7 +2304,7 @@
       </c>
       <c r="H3" s="39" t="inlineStr">
         <is>
-          <t>Stress change fine-to-medium &lt;2% claimed; coarse-to-fine range ~6%; non-monotonic sequence (238, 226, 241 MPa)</t>
+          <t>Fine-to-medium peak stress change &lt;2% for tip deflection; peak stress values non-monotonic across all three levels (238, 226, 241 MPa); extrapolated value 244 MPa; ~6% spread coarse-to-fine</t>
         </is>
       </c>
       <c r="I3" s="42" t="inlineStr">
@@ -2311,7 +2316,7 @@
     <row r="4" ht="15" customHeight="1" s="18">
       <c r="A4" s="41" t="inlineStr">
         <is>
-          <t>Modal Frequency Correlation</t>
+          <t>Modal Frequency Correlation with Shaker Test</t>
         </is>
       </c>
       <c r="B4" s="41" t="inlineStr">
@@ -2322,12 +2327,12 @@
       <c r="C4" s="33" t="n"/>
       <c r="D4" s="41" t="inlineStr">
         <is>
-          <t>Predicted natural frequencies from linear perturbation FEA compared against shaker test measurements on full bracket with mass simulator. Symmetry was used in the model but not in the test.</t>
+          <t>Predicted natural frequencies from linear perturbation FEA compared against laboratory shaker test measurements on the full bracket with helicoils and Belleville washers. FEA used symmetry half-model with tied interfaces; test used full bracket.</t>
         </is>
       </c>
       <c r="E4" s="41" t="inlineStr">
         <is>
-          <t>Shaker test measured frequencies (f1=770±8 Hz, f2=1130 Hz, f3=1592 Hz)</t>
+          <t>Measured f1=770±8 Hz, f2=1130 Hz, f3=1592 Hz</t>
         </is>
       </c>
       <c r="F4" s="41" t="inlineStr">
@@ -2337,12 +2342,12 @@
       </c>
       <c r="G4" s="41" t="inlineStr">
         <is>
-          <t>Test measurement uncertainty (±8 Hz on f1); sensitivity to contact assumption (tied vs slip: f1 912 vs 828 Hz)</t>
+          <t>Test measurement uncertainty stated as ±8 Hz for f1; sensitivity study (bolt torque ±10%, E −5%) provides parametric bounds</t>
         </is>
       </c>
       <c r="H4" s="41" t="inlineStr">
         <is>
-          <t>f1 error ~18% (912 vs 770 Hz) baseline; ~7% if joint-slip trial (828 vs 770 Hz) used; f2 error ~4.7%; f3 error ~3.0%</t>
+          <t>f1 error ~18% (912 vs 770 Hz); f2 error ~4.7% (1183 vs 1130 Hz); f3 error ~3.0% (1640 vs 1592 Hz); joint-slip trial f1=828 Hz reduces f1 error to ~7%</t>
         </is>
       </c>
       <c r="I4" s="42" t="inlineStr">
@@ -2354,7 +2359,7 @@
     <row r="5" ht="15" customHeight="1" s="18">
       <c r="A5" s="41" t="inlineStr">
         <is>
-          <t>Static Strain Gauge Correlation</t>
+          <t>Static Strain-Gage Correlation</t>
         </is>
       </c>
       <c r="B5" s="41" t="inlineStr">
@@ -2365,12 +2370,12 @@
       <c r="C5" s="33" t="n"/>
       <c r="D5" s="41" t="inlineStr">
         <is>
-          <t>FEA-predicted strain at two locations compared against strain gauge measurements from static pull test at 15 g equivalent load.</t>
+          <t>FEA-predicted strain at two gage locations (SG-03 at lower hole quadrant, SG-07 on web) compared against measured strains from static pull test at 15 g equivalent loading.</t>
         </is>
       </c>
       <c r="E5" s="41" t="inlineStr">
         <is>
-          <t>Strain gauge SG-03 (310 με) and SG-07 (190 με) from static pull test</t>
+          <t>SG-03 test 310 με; SG-07 test 190 με</t>
         </is>
       </c>
       <c r="F5" s="41" t="inlineStr">
@@ -2381,7 +2386,7 @@
       <c r="G5" s="33" t="n"/>
       <c r="H5" s="41" t="inlineStr">
         <is>
-          <t>SG-03: FEA (linear elastic) 285 με vs test 310 με = 8.1% low; SG-07: FEA 195 με vs test 190 με = 2.6% high; plasticity model worsens SG-03 correlation (342 με predicted)</t>
+          <t>SG-03: FEA (linear elastic) 285 με, error −8.1%; SG-03 with plasticity 342 με (overcorrects); SG-07: FEA 195 με vs test 190 με, error +2.6%</t>
         </is>
       </c>
       <c r="I5" s="42" t="inlineStr">
@@ -2404,12 +2409,12 @@
       <c r="C6" s="33" t="n"/>
       <c r="D6" s="41" t="inlineStr">
         <is>
-          <t>Parametric sensitivity of peak stress and first natural frequency to bolt torque, fillet radius, elastic modulus, and contact friction, varied one parameter at a time on the medium mesh.</t>
+          <t>Parametric sensitivity of peak stress and first natural frequency to bolt torque, fillet radius, elastic modulus, and contact friction coefficient, varied one-at-a-time on the medium mesh.</t>
         </is>
       </c>
       <c r="E6" s="41" t="inlineStr">
         <is>
-          <t>Baseline medium mesh results</t>
+          <t>Baseline medium mesh predictions</t>
         </is>
       </c>
       <c r="F6" s="41" t="inlineStr">
@@ -2424,7 +2429,7 @@
       </c>
       <c r="H6" s="41" t="inlineStr">
         <is>
-          <t>Bolt torque ±10% → peak stress ±6%, f1 ±3%; fillet -0.2 mm → stress +7%; E -5% → f1 -2.6%, strain +3.1%; friction 0.2→0.1 → stress +4%</t>
+          <t>Bolt torque ±10% → peak stress ±6%, f1 ±3%; fillet radius −0.2 mm → peak stress +7%; E −5% → f1 −2.6%, strain +3.1%; friction 0.2→0.1 → peak stress +4%</t>
         </is>
       </c>
       <c r="I6" s="42" t="inlineStr">
@@ -2654,16 +2659,16 @@
         <v>3</v>
       </c>
       <c r="D5" s="41" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E5" s="42" t="inlineStr">
         <is>
-          <t>Commercial solver with documented QA, version control, and regression testing; consistent solver version across all runs.</t>
+          <t>Commercial solver with documented version control and release qualification</t>
         </is>
       </c>
       <c r="F5" s="41" t="inlineStr">
         <is>
-          <t>Abaqus/Standard is a commercial solver with established QA processes. The project uses Git LFS for model and results archiving (commit 7f1a9c3) and a Python build script for reproducibility. However, the study mixes two solver versions (2022 HF4 for early coarse/medium runs and 2023 HF7 for fine/nonlinear runs), and contact stabilization defaults differ between versions. No explicit regression test suite or version-lock policy is documented for this project. The mixed-version run set undermines confidence in software QA at the project level.</t>
+          <t>Abaqus/Standard 2023 HF7 is a commercial, widely-validated FEA solver. The report identifies specific hotfix versions (2023 HF7 primary, 2022 HF4 for early runs) and notes model files are stored in Git LFS (commit 7f1a9c3) with a Python build script (build_avb21.py). However, mixing two solver versions in the convergence dataset (contact stabilization defaults differ between them) is a documented gap. No explicit regression test suite or ISO 9001 certification evidence is cited.</t>
         </is>
       </c>
       <c r="G5" s="41" t="inlineStr">
@@ -2691,12 +2696,12 @@
       </c>
       <c r="E6" s="42" t="inlineStr">
         <is>
-          <t>Governing equations verified against known benchmarks or analytical solutions for representative structural configurations.</t>
+          <t>Solver benchmarked against known analytical or reference solutions for relevant physics</t>
         </is>
       </c>
       <c r="F6" s="41" t="inlineStr">
         <is>
-          <t>No explicit benchmark or method of manufactured solutions (MMS) study is reported for this project. Abaqus/Standard is a widely used commercial code with extensive published verification benchmarks in its documentation, providing baseline confidence. No project-specific code verification against analytical solutions for an L-bracket or bolted joint was referenced. Credit is given for use of a well-established commercial solver, but no supplementary numerical code verification is documented in the evidence.</t>
+          <t>No benchmark problems, method of manufactured solutions, or analytical comparisons are presented in the evidence. Abaqus/Standard is a widely-used commercial code with published element verification, but no project-specific code verification activity is documented. Reliance is entirely on the commercial solver's reputation.</t>
         </is>
       </c>
       <c r="G6" s="41" t="inlineStr">
@@ -2724,12 +2729,12 @@
       </c>
       <c r="E7" s="42" t="inlineStr">
         <is>
-          <t>Monotonically converging mesh refinement sequence with GCI or Richardson extrapolation quantifying discretization error; consistent element types and solver settings across refinement levels.</t>
+          <t>Monotonic mesh convergence demonstrated; GCI or Richardson extrapolation reported with adequate refinement ratio</t>
         </is>
       </c>
       <c r="F7" s="41" t="inlineStr">
         <is>
-          <t>A three-level mesh convergence study was performed (78k, 164k, 512k elements) with Richardson extrapolation applied to the medium/fine pair. However, the peak von Mises stress sequence is non-monotonic (238, 226, 241 MPa), contradicting the claim of monotonic convergence. Early coarse and medium runs were performed in Abaqus 2022 HF4 while fine runs used 2023 HF7, with differing NLGEOM settings (NLGEOM=NO for medium mesh in internal log) and different contact stabilization defaults. One mesh seed (hole-edge 0.45 mm) was set manually and not captured in the build script. Tip deflection converged acceptably. The inconsistencies in solver settings and non-monotonic stress sequence substantially reduce confidence in the discretization error estimate.</t>
+          <t>A three-level mesh refinement study is documented (78k, 164k, 512k elements). Richardson extrapolation was applied to the medium/fine pair, yielding an extrapolated peak stress of 244 MPa. However, the convergence is explicitly non-monotonic across all three levels (238, 226, 241 MPa), which violates the stated claim of monotonic convergence. The coarse and medium meshes were run in a different solver version (2022 HF4) with different stabilization defaults, further undermining the study. Tip deflection converged, but stress — the primary QoI — did not demonstrate clean monotonic convergence. No formal GCI is reported.</t>
         </is>
       </c>
       <c r="G7" s="41" t="inlineStr">
@@ -2757,12 +2762,12 @@
       </c>
       <c r="E8" s="42" t="inlineStr">
         <is>
-          <t>Documented residual convergence targets, iteration monitoring, and consistent use of nonlinear solution controls across all runs.</t>
+          <t>Residual convergence targets documented; iterative solver settings recorded per run</t>
         </is>
       </c>
       <c r="F8" s="41" t="inlineStr">
         <is>
-          <t>Automatic stabilization (1e-4) was used for two increments to suppress contact chattering and then turned off. Large-deflection flag (NLGEOM) was ON for static load step in the production description, but internal log shows NLGEOM=NO was used for the medium mesh to improve convergence. A run deck note (v3.2) states pretension was dropped after step 2 due to divergence, with bolts tied instead, contradicting the pretension description. No explicit residual targets or convergence history plots are reported. These contradictions indicate solver settings were not consistently applied or documented.</t>
+          <t>Some solver settings are mentioned: automatic stabilization factor 1e-4 used for two increments and then turned off, large-deflection flag ON for static steps. However, there is a documented contradiction — early runs used NLGEOM=NO on the medium mesh, and a run deck note states bolts were tied after step 2 due to divergence. Residual convergence criteria and iteration counts are not explicitly reported. The inconsistencies between run decks reduce confidence.</t>
         </is>
       </c>
       <c r="G8" s="41" t="inlineStr">
@@ -2790,12 +2795,12 @@
       </c>
       <c r="E9" s="42" t="inlineStr">
         <is>
-          <t>Independent review of boundary conditions, loads, contact definitions, material assignments, and post-processing; documented reconciliation of all model setup choices.</t>
+          <t>Independent review of model setup, boundary conditions, mesh quality, and post-processing confirmed</t>
         </is>
       </c>
       <c r="F9" s="41" t="inlineStr">
         <is>
-          <t>No independent technical review of the model setup is documented. Multiple internal contradictions are present and unresolved: (1) linear elastic vs bilinear plastic material model inconsistently applied across runs and slides; (2) NLGEOM=NO used in some runs contradicting the stated NLGEOM=ON policy; (3) pretension claimed active through load steps but run deck shows bolts tied after step 2; (4) symmetry used in modal model but not in test; (5) temperature-independent data stated for static runs but temperature-dependent E stated elsewhere. The executive summary reports FoS 1.35 from the joint-slip trial rather than the baseline fine mesh. These unresolved contradictions indicate significant risk of use error that has not been caught or corrected.</t>
+          <t>Multiple setup errors and internal contradictions are documented and unresolved: (1) symmetry used in FEA but not in test; (2) pretension claimed active but a run deck note states bolts were tied after step 2; (3) NLGEOM inconsistency across mesh levels; (4) linear elastic stress referenced in the executive summary while plasticity was also run; (5) one manual mesh seed not captured in the build script; (6) summary table drawn from mixed 2022/2023 solver runs; (7) FoS of 1.35 in executive summary appears to reference the joint-slip trial rather than the baseline. No evidence of independent model review is cited.</t>
         </is>
       </c>
       <c r="G9" s="41" t="inlineStr">
@@ -2823,12 +2828,12 @@
       </c>
       <c r="E10" s="42" t="inlineStr">
         <is>
-          <t>Justified selection of element types, contact formulations, plasticity model, and modal analysis approach with documented known limitations.</t>
+          <t>Governing equations and constitutive models justified for the loading regime; known limitations documented</t>
         </is>
       </c>
       <c r="F10" s="41" t="inlineStr">
         <is>
-          <t>The choice of C3D10M quadratic tets with curvature control is reasonable for stress concentration regions. Bilinear kinematic hardening calibrated to ASTM E8 coupons is documented. Modal linear perturbation about prestressed state is an appropriate approach. Known limitations are partially documented (no fretting fatigue, no thermal gradients in static, random vibration out of scope). However, the inconsistent application of the plasticity model across runs, the unexplained drop to linear elastic in some results, the use of symmetry that does not match test boundary conditions, and the unresolved contact representation (pretension vs tied bolts) indicate the model form is not consistently or fully justified. Sensitivity to contact assumption (f1 change of ~10%) is noted but not resolved.</t>
+          <t>The choice of continuum FEA with C3D10M elements is appropriate for the geometry. Bilinear kinematic plasticity calibrated to ASTM E8 coupons is documented, and the Ramberg-Osgood parameters are stated. Temperature-dependent modulus is used for modal analysis with MIL-HDBK-5 data. However, model form limitations are only partially addressed: no fretting, no shock, no random vibration (scoped out). The contradiction between linear-elastic and nonlinear analyses being used interchangeably in the same results summary, and the inconsistent joint representation (pretension vs tied), indicate model form choices are not fully controlled or justified.</t>
         </is>
       </c>
       <c r="G10" s="41" t="inlineStr">
@@ -2856,12 +2861,12 @@
       </c>
       <c r="E11" s="42" t="inlineStr">
         <is>
-          <t>Material properties from traceable testing, geometry from measured as-built dimensions, boundary conditions and loads from documented sources with uncertainty characterization.</t>
+          <t>Material properties from traceable testing; geometry from measured as-built dimensions; boundary conditions characterized with uncertainty</t>
         </is>
       </c>
       <c r="F11" s="41" t="inlineStr">
         <is>
-          <t>Elastic modulus and yield strength are from AMS 4045 material specification. Bilinear plasticity is calibrated from in-house ASTM E8 coupons with Ramberg-Osgood parameters documented. Temperature-dependent E is from MIL-HDBK-5. Load distribution (60/40 front-to-rear) is stated but source not given. Bolt pretension from design torque (5.7 N·m → ~8 kN) is documented. As-built differences are noted: measured hole diameters (5.62-5.66 mm) differ from nominal (5.5 mm) used in FEA; Belleville washers and helicoils present in test but absent from model; friction coefficient (0.2) not calibrated by torque-tension test. Input uncertainty is partially characterized through sensitivity study but not formally propagated. Several as-built deviations from the model are acknowledged but not corrected.</t>
+          <t>Elastic and plastic material properties are sourced from in-house ASTM E8 coupons and AMS 4045, which is reasonable. Temperature-dependent E is from MIL-HDBK-5. However, measured hole diameters (5.62–5.66 mm vs nominal 5.5 mm) were not incorporated into the FEA model — nominal values were used. Helicoils and Belleville washers present in the test article are absent from the analysis model. Friction coefficient (0.2) is assumed, not measured from a torque-tension coupon (identified as a gap). Load sharing (60/40 front-to-rear) is stated without measurement basis. These gaps collectively reduce confidence in input fidelity.</t>
         </is>
       </c>
       <c r="G11" s="41" t="inlineStr">
@@ -2889,12 +2894,12 @@
       </c>
       <c r="E12" s="42" t="inlineStr">
         <is>
-          <t>Test article representative of production design, with documented as-built configuration and sufficient specimens for statistical characterization.</t>
+          <t>Test article is production-representative with documented configuration control</t>
         </is>
       </c>
       <c r="F12" s="41" t="inlineStr">
         <is>
-          <t>One physical bracket was used for both shaker and static pull tests (implied by single dataset). The test article included helicoils and Belleville washers per process sheet, which are production-representative for those features. However, only a single specimen is apparent from the evidence; no statistical characterization across multiple specimens is reported. As-built hole diameters (5.62-5.66 mm) were measured for the test lot, providing some geometric characterization. The single-specimen approach limits statistical confidence.</t>
+          <t>One test article is described (full bracket with mass simulator, four bolts at design torque, helicoils and Belleville washers per process sheet). The test article is described as production-representative in terms of fastener installation. However, only a single specimen is evidenced, sample size justification is absent, and the as-built differences (helicoils optional per drawing, Belleville washers not in analysis) are noted but not fully reconciled. No statistical characterization of the test lot hardware is provided beyond hole diameter measurements on the test lot (5.62–5.66 mm).</t>
         </is>
       </c>
       <c r="G12" s="41" t="inlineStr">
@@ -2922,12 +2927,12 @@
       </c>
       <c r="E13" s="42" t="inlineStr">
         <is>
-          <t>Calibrated instrumentation, controlled and documented test environment, measurement uncertainty reported, test conducted to recognized standards.</t>
+          <t>Calibrated instrumentation, controlled environment, measurement uncertainty reported, traceable to standards</t>
         </is>
       </c>
       <c r="F13" s="41" t="inlineStr">
         <is>
-          <t>Shaker test conducted at ambient temperature (21°C) with bolts torqued to specification (5.7 N·m). Measurement uncertainty on f1 is reported (±8 Hz). Strain gauges used for static correlation. However, no calibration records for instrumentation are cited, no formal test standard (e.g., MIL-STD-810, ASTM) is referenced for the shaker or pull test, and environmental control beyond ambient temperature is not documented. The test setup used full bracket with mass simulator, which is appropriate, but fixture compliance from Belleville washers vs model flat washer disks is noted as an uncontrolled difference.</t>
+          <t>Shaker test conditions are partially documented: bolt torque 5.7 N·m, ambient temperature 21 C, four-bolt configuration with washers and helicoils. Measurement uncertainty for f1 is stated as ±8 Hz. Static strain-gage readings are reported at two locations. However, instrument calibration records, test facility standards (e.g., ISO 5344 or equivalent), environmental control details, and data acquisition settings are not described. The fixture configuration difference (full bracket in test vs symmetry model in FEA) is noted but not quantified as a test condition uncertainty.</t>
         </is>
       </c>
       <c r="G13" s="41" t="inlineStr">
@@ -2955,12 +2960,12 @@
       </c>
       <c r="E14" s="42" t="inlineStr">
         <is>
-          <t>Model inputs demonstrably matched to test conditions for the validation comparison; boundary condition differences identified and their effect quantified.</t>
+          <t>Model inputs demonstrably match test conditions; discrepancies quantified and bounded</t>
         </is>
       </c>
       <c r="F14" s="41" t="inlineStr">
         <is>
-          <t>There are multiple known and unresolved mismatches between model and test: (1) model uses symmetry boundary condition; test uses full bracket — this is a fundamental configurational mismatch for modal correlation; (2) model omits Belleville washers; test article includes them, adding compliance likely responsible for part of the 18% f1 discrepancy; (3) model uses nominal hole diameter (5.5 mm); test lot measured 5.62-5.66 mm; (4) bolt pretension treatment is inconsistent (tied vs active pretension) between runs; (5) temperature at test (21°C) vs model reference (20°C) is close but not formally reconciled. The slide deck acknowledges these mismatches but does not quantify their combined effect or rerun a matched configuration prior to reporting results.</t>
+          <t>Several significant mismatches between model and test configurations are documented and unresolved: (1) FEA uses symmetry half-model; test uses full bracket; (2) FEA omits Belleville washers; test includes them (identified as a likely compliance contributor to f1 discrepancy); (3) FEA uses nominal hole diameters; test lot holes are 2–3% oversized; (4) pretension handling is inconsistent across run decks; (5) helicoil compliance absent from model. The sensitivity study provides some bounds on individual parameters but no systematic propagation of all input discrepancies to output uncertainty is performed.</t>
         </is>
       </c>
       <c r="G14" s="41" t="inlineStr">
@@ -2988,12 +2993,12 @@
       </c>
       <c r="E15" s="42" t="inlineStr">
         <is>
-          <t>Quantitative comparison of model predictions to test data with error metrics, uncertainty bands, and assessment against acceptance criteria for all QoIs.</t>
+          <t>Quantitative comparison metrics reported for all primary QoIs; uncertainty bands included; claims consistent with underlying data</t>
         </is>
       </c>
       <c r="F15" s="41" t="inlineStr">
         <is>
-          <t>Quantitative comparisons are provided: f1 18% error (baseline) or 7% (joint-slip trial); f2 ~4.7% error; f3 ~3.0% error; SG-03 strain 8.1% low (linear elastic) or overpredicted with plasticity; SG-07 strain 2.6% high. The slide deck reports "within 5% of prediction" for modes, which is incorrect for f1 against the baseline model. The modal clearance to the payload bay line is only 2.7% by test vs 21% claimed by analysis — a critical discrepancy for the acceptance decision. Uncertainty bands are partially provided (±8 Hz on f1). Comparison is complicated by the mixed model configurations (which run corresponds to which comparison point is not always clear). No formal validation metric (e.g., U95 band overlap, ASME V&amp;V 10 validation metric) is computed.</t>
+          <t>Quantitative comparisons are reported for strain gages (SG-03: −8.1% error; SG-07: +2.6% error) and natural frequencies (f1: ~18% error, f2: ~4.7%, f3: ~3.0%). However, the summary claim of "within 5% of prediction" for f1 is inconsistent with the underlying data (18% discrepancy relative to the baseline model). The static FoS summary line ("minimum FoS 1.35 at fillet") appears to reference a different run configuration than the reported fine-mesh result. Uncertainty bands are partial (±8 Hz for f1 only). The mixed-run provenance of the summary table further reduces confidence in the reported comparisons.</t>
         </is>
       </c>
       <c r="G15" s="41" t="inlineStr">
@@ -3021,12 +3026,12 @@
       </c>
       <c r="E16" s="42" t="inlineStr">
         <is>
-          <t>QoIs directly address the safety and qualification requirements; both computationally predictable and experimentally measurable.</t>
+          <t>QoIs (peak stress/FoS and natural frequencies) directly address the safety and qualification requirements and are measurable both computationally and experimentally</t>
         </is>
       </c>
       <c r="F16" s="41" t="inlineStr">
         <is>
-          <t>The two primary QoIs — peak von Mises stress (yield margin) and natural frequencies (modal clearance) — are directly relevant to the structural qualification requirements. Both are standard structural QoIs that are well-defined computationally and measurable experimentally via strain gauges and accelerometers/shaker tests. The strain gauge comparison provides a direct link between predicted and measured local stress state. Modal frequencies are the direct measure for payload bay clearance requirements. QoI selection is appropriate and relevant to the decision.</t>
+          <t>The primary QoIs — peak von Mises stress (yielding margin) and first three natural frequencies (payload bay clearance) — are directly relevant to the stated qualification requirements and are computed by the FEA and measured in the shaker and pull tests. Strain at gage locations provides a secondary surrogate for local stress. The QoIs are well-chosen for the context of use, though random vibration response and shock are explicitly scoped out as separate future activities.</t>
         </is>
       </c>
       <c r="G16" s="41" t="inlineStr">
@@ -3054,12 +3059,12 @@
       </c>
       <c r="E17" s="42" t="inlineStr">
         <is>
-          <t>Validation conditions (geometry, loading, boundary conditions, environment) match the intended use conditions; gaps between validation and COU envelope are identified and addressed.</t>
+          <t>Validation conditions (geometry, loading, boundary conditions, environment) sufficiently represent the intended launch vehicle operational and qualification envelope</t>
         </is>
       </c>
       <c r="F17" s="41" t="inlineStr">
         <is>
-          <t>The shaker test and static pull test use the actual bracket hardware under representative loading conditions, which is directly relevant to the COU. However, significant gaps between validation activities and COU exist: (1) the modal test used full bracket while the model used symmetry — the validation activity does not cover the same configurational assumption as the analysis model; (2) the static test was conducted at ambient temperature while the COU spans -20 to +50°C; temperature effects on modes were swept parametrically but not validated; (3) random vibration response and shock are out of scope for this phase but are part of the launch environment; (4) the Belleville washer and helicoil configuration tested differs from the model. These gaps are acknowledged in the recommendations but not resolved prior to the assessment.</t>
+          <t>The shaker test and static pull test address the same physical phenomena (modal response, local strain under quasi-static load) as the intended use. However, several gaps exist: (1) the test fixture uses the full bracket while the validated model uses a symmetry half-model, creating a geometric non-equivalence; (2) Belleville washers and helicoils are present in the test but absent from the model, meaning the validated configuration does not match the analysis configuration; (3) the temperature range (−20 to +50 C) is not validated — only ambient 21 C testing is performed; (4) random vibration and shock environments are explicitly out of scope. These gaps limit the extent to which the validation activities cover the full COU envelope.</t>
         </is>
       </c>
       <c r="G17" s="41" t="inlineStr">
@@ -3148,7 +3153,7 @@
       </c>
       <c r="B3" s="39" t="inlineStr">
         <is>
-          <t>The model and validation study as documented contain multiple unresolved deficiencies that prevent acceptance for design freeze decisions. Critical issues include: (1) the primary QoI for modal clearance — the 10% separation from the 750 Hz payload bay notch — is met by only 2.7% margin in test (f1=770 Hz measured vs 750 Hz limit), whereas the analysis predicted 21% clearance, a factor-of-eight overestimate of the safety margin; (2) the f1 prediction error is 18% against the baseline model configuration, exceeding typical structural validation tolerances; (3) fundamental contradictions in model setup (NLGEOM flag, pretension vs tied bolts, linear vs nonlinear material) across reported runs have not been reconciled, so it is unclear which model configuration produced which reported result; (4) the mesh convergence sequence is non-monotonic and the Richardson extrapolation is based on only two mesh levels run with differing solver settings and software versions; (5) the executive summary FoS (1.35) references the joint-slip trial rather than the baseline fine mesh without disclosure. Acceptance is withheld pending completion of the open items on Slide 13-14: unified re-run with consistent solver version and settings, removal of symmetry for modal correlation, inclusion of Belleville washer compliance, and correction of all summary tables to reflect matched configurations. If re-analysis demonstrates consistent FoS &gt;1.25 and modal clearance &gt;10% from the payload bay line with validated model, the model may be accepted.</t>
+          <t>The model is not accepted in its current state for design freeze or formal qualification use. Critical deficiencies preclude acceptance: (1) The primary modal QoI (f1) shows an ~18% discrepancy between the baseline FEA (912 Hz) and test (770 Hz), reducing the actual clearance to the 750 Hz payload line to only 2.7% by test — far below the 10% required — whereas the analysis claimed 21% clearance. This is a direct failure against the stated qualification requirement. (2) Multiple unresolved internal contradictions exist in the model documentation (pretension vs tied bolts, NLGEOM inconsistency, linear vs nonlinear stress in summary, mixed solver versions in convergence dataset, unsupported executive summary FoS claim). (3) The test and model configurations are not equivalent (symmetry, washers, helicoils), and input discrepancies have not been quantified or bounded. (4) The mesh convergence study is non-monotonic and cannot support the Richardson extrapolation claim. The recommendations in Slides 13–14 define a clear remediation path: unify the run set in a single solver version, remove symmetry for modal correlation, incorporate Belleville washer and helicoil compliance, reconcile material model usage, and restate all summary metrics against equivalent configurations. The model may be accepted following completion and documented closure of these open items.</t>
         </is>
       </c>
       <c r="C3" s="22" t="inlineStr">
@@ -3158,7 +3163,7 @@
       </c>
       <c r="D3" s="39" t="inlineStr">
         <is>
-          <t>Assessment derived from E. Chen / structures team documentation</t>
+          <t>E. Chen / J. Patel (structures and test leads, per Slide 1 team list)</t>
         </is>
       </c>
       <c r="E3" s="22" t="n"/>
